--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_tarapaca.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:31</t>
+    <t xml:space="preserve">2026-09-24 01:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -568,7 +568,7 @@
         <v>-0.15</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -584,10 +584,10 @@
         <v>5</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.25</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G3" s="2"/>
     </row>
@@ -606,7 +606,7 @@
         <v>-0.05</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G4" s="2"/>
     </row>
@@ -625,7 +625,7 @@
         <v>0.22</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G5" s="2"/>
     </row>
@@ -644,7 +644,7 @@
         <v>0.26</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G6" s="2"/>
     </row>
@@ -656,19 +656,19 @@
         <v>14</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="8">
@@ -679,19 +679,19 @@
         <v>14</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-0.41</v>
+        <v>-0.38</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="9">
@@ -702,19 +702,19 @@
         <v>14</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-0.52</v>
+        <v>-0.49</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="10">
@@ -729,10 +729,10 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G10" s="2"/>
     </row>
@@ -748,10 +748,10 @@
         <v>2</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G11" s="2"/>
     </row>
@@ -763,19 +763,19 @@
         <v>14</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-0.61</v>
+        <v>-0.62</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-0.73</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="13">
@@ -792,13 +792,13 @@
         <v>6</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.81</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="14">
@@ -815,13 +815,13 @@
         <v>6</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="15">
@@ -838,13 +838,13 @@
         <v>6</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="16">
@@ -855,19 +855,19 @@
         <v>14</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E16" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>325</v>
+      </c>
+      <c r="G16" s="2" t="n">
         <v>0.1</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>322</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>0.09</v>
       </c>
     </row>
     <row r="17">
@@ -884,13 +884,13 @@
         <v>7</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="18">
@@ -908,7 +908,7 @@
         <v>-0.41</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G18" s="2"/>
     </row>
@@ -929,10 +929,10 @@
         <v>-0.2</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="20">
@@ -949,13 +949,13 @@
         <v>6</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="21">
@@ -966,7 +966,7 @@
         <v>31</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.41</v>
+        <v>-0.4</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>7</v>
@@ -975,10 +975,10 @@
         <v>0.06</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.47</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="22">
@@ -989,19 +989,19 @@
         <v>31</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="23">
@@ -1012,19 +1012,19 @@
         <v>31</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.54</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.53</v>
+        <v>-0.52</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_tarapaca.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:21</t>
+    <t xml:space="preserve">2026-10-01 23:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_tarapaca.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:21</t>
+    <t xml:space="preserve">2026-10-05 19:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
